--- a/Documents/Qualified Entities and Attributes.xlsx
+++ b/Documents/Qualified Entities and Attributes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\My Works\ORBIX BUSINESS\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F0B45C0-D460-40B1-92B9-AE59FDBFA98D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC66AEF3-DF64-49A2-A805-DBE41D42E23D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11640" yWindow="1605" windowWidth="8775" windowHeight="7785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="66">
   <si>
     <t>System</t>
   </si>
@@ -214,6 +214,15 @@
   </si>
   <si>
     <t>Imp WebFE</t>
+  </si>
+  <si>
+    <t>legalType</t>
+  </si>
+  <si>
+    <t>foundingDate</t>
+  </si>
+  <si>
+    <t>date</t>
   </si>
 </sst>
 </file>
@@ -255,10 +264,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -540,10 +549,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H175"/>
+  <dimension ref="A1:H177"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.140625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="15.140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="13.28515625" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.42578125" style="1" customWidth="1"/>
@@ -552,7 +561,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -578,27 +587,27 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -612,7 +621,7 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -626,7 +635,7 @@
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -640,7 +649,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -654,7 +663,7 @@
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -668,7 +677,7 @@
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -688,7 +697,7 @@
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -699,419 +708,435 @@
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+      <c r="B18" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+      <c r="B19" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
+      <c r="B20" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
+      <c r="B21" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
+      <c r="B22" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
+      <c r="B23" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+      <c r="B24" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
+      <c r="B25" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
+      <c r="B26" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
+      <c r="B27" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B28" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
+      <c r="C28" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B29" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
+      <c r="C29" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B30" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C28" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="2" t="s">
+      <c r="C30" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="2" t="s">
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B53" s="2"/>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
-      <c r="E53" s="2"/>
-      <c r="F53" s="2"/>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="2" t="s">
+      <c r="B55" s="3"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B61" s="2"/>
-      <c r="C61" s="2"/>
-      <c r="D61" s="2"/>
-      <c r="E61" s="2"/>
-      <c r="F61" s="2"/>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="2" t="s">
+      <c r="B63" s="3"/>
+      <c r="C63" s="3"/>
+      <c r="D63" s="3"/>
+      <c r="E63" s="3"/>
+      <c r="F63" s="3"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B72" s="2"/>
-      <c r="C72" s="2"/>
-      <c r="D72" s="2"/>
-      <c r="E72" s="2"/>
-      <c r="F72" s="2"/>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="2" t="s">
+      <c r="B74" s="3"/>
+      <c r="C74" s="3"/>
+      <c r="D74" s="3"/>
+      <c r="E74" s="3"/>
+      <c r="F74" s="3"/>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B85" s="2"/>
-      <c r="C85" s="2"/>
-      <c r="D85" s="2"/>
-      <c r="E85" s="2"/>
-      <c r="F85" s="2"/>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A95" s="2" t="s">
+      <c r="B87" s="3"/>
+      <c r="C87" s="3"/>
+      <c r="D87" s="3"/>
+      <c r="E87" s="3"/>
+      <c r="F87" s="3"/>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B95" s="2"/>
-      <c r="C95" s="2"/>
-      <c r="D95" s="2"/>
-      <c r="E95" s="2"/>
-      <c r="F95" s="2"/>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A96" s="3" t="s">
+      <c r="B97" s="3"/>
+      <c r="C97" s="3"/>
+      <c r="D97" s="3"/>
+      <c r="E97" s="3"/>
+      <c r="F97" s="3"/>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B96" s="1" t="s">
+      <c r="B98" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C96" s="1">
+      <c r="C98" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A97" s="3" t="s">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A98" s="3" t="s">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A99" s="3" t="s">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A100" s="3" t="s">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A101" s="3" t="s">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A102" s="3" t="s">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A103" s="3" t="s">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A104" s="3" t="s">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A105" s="3" t="s">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A106" s="3" t="s">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" s="2" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A113" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B113" s="2"/>
-      <c r="C113" s="2"/>
-      <c r="D113" s="2"/>
-      <c r="E113" s="2"/>
-      <c r="F113" s="2"/>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A114" s="3" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B115" s="3"/>
+      <c r="C115" s="3"/>
+      <c r="D115" s="3"/>
+      <c r="E115" s="3"/>
+      <c r="F115" s="3"/>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A116" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A116" s="3" t="s">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A117" s="3" t="s">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A119" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A118" s="3" t="s">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A120" s="2" t="s">
         <v>33</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A124" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B124" s="2"/>
-      <c r="C124" s="2"/>
-      <c r="D124" s="2"/>
-      <c r="E124" s="2"/>
-      <c r="F124" s="2"/>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A125" s="3" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B126" s="3"/>
+      <c r="C126" s="3"/>
+      <c r="D126" s="3"/>
+      <c r="E126" s="3"/>
+      <c r="F126" s="3"/>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A127" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A128" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A137" s="2" t="s">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A139" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B137" s="2"/>
-      <c r="C137" s="2"/>
-      <c r="D137" s="2"/>
-      <c r="E137" s="2"/>
-      <c r="F137" s="2"/>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A150" s="2" t="s">
+      <c r="B139" s="3"/>
+      <c r="C139" s="3"/>
+      <c r="D139" s="3"/>
+      <c r="E139" s="3"/>
+      <c r="F139" s="3"/>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A152" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B150" s="2"/>
-      <c r="C150" s="2"/>
-      <c r="D150" s="2"/>
-      <c r="E150" s="2"/>
-      <c r="F150" s="2"/>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A164" s="2" t="s">
+      <c r="B152" s="3"/>
+      <c r="C152" s="3"/>
+      <c r="D152" s="3"/>
+      <c r="E152" s="3"/>
+      <c r="F152" s="3"/>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A166" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B164" s="2"/>
-      <c r="C164" s="2"/>
-      <c r="D164" s="2"/>
-      <c r="E164" s="2"/>
-      <c r="F164" s="2"/>
-    </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A175" s="2" t="s">
+      <c r="B166" s="3"/>
+      <c r="C166" s="3"/>
+      <c r="D166" s="3"/>
+      <c r="E166" s="3"/>
+      <c r="F166" s="3"/>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A177" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B175" s="2"/>
-      <c r="C175" s="2"/>
-      <c r="D175" s="2"/>
-      <c r="E175" s="2"/>
-      <c r="F175" s="2"/>
+      <c r="B177" s="3"/>
+      <c r="C177" s="3"/>
+      <c r="D177" s="3"/>
+      <c r="E177" s="3"/>
+      <c r="F177" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A150:F150"/>
-    <mergeCell ref="A164:F164"/>
-    <mergeCell ref="A175:F175"/>
-    <mergeCell ref="A72:F72"/>
-    <mergeCell ref="A85:F85"/>
-    <mergeCell ref="A95:F95"/>
-    <mergeCell ref="A113:F113"/>
-    <mergeCell ref="A124:F124"/>
-    <mergeCell ref="A137:F137"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A43:F43"/>
-    <mergeCell ref="A53:F53"/>
-    <mergeCell ref="A61:F61"/>
+    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A55:F55"/>
+    <mergeCell ref="A63:F63"/>
+    <mergeCell ref="A152:F152"/>
+    <mergeCell ref="A166:F166"/>
+    <mergeCell ref="A177:F177"/>
+    <mergeCell ref="A74:F74"/>
+    <mergeCell ref="A87:F87"/>
+    <mergeCell ref="A97:F97"/>
+    <mergeCell ref="A115:F115"/>
+    <mergeCell ref="A126:F126"/>
+    <mergeCell ref="A139:F139"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
